--- a/Findings/Q3_Total_Orders.xlsx
+++ b/Findings/Q3_Total_Orders.xlsx
@@ -3,24 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4AC385-04D3-4F2F-835E-5A37EB504A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A520E8C7-7A21-412D-8FFB-4CD845164E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="SQL" sheetId="2" r:id="rId2"/>
-    <sheet name="Visual" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
-  <si>
-    <t>total_customers</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>total_orders</t>
   </si>
@@ -28,8 +24,7 @@
     <t>Page 1</t>
   </si>
   <si>
-    <t>SELECT DISTINCT COUNT(CustomerID) AS total_customers,
-COUNT(OrderID) AS total_orders
+    <t>SELECT DISTINCT COUNT(OrderID) AS total_orders
 FROM Orders;</t>
   </si>
 </sst>
@@ -37,7 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -49,15 +44,10 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -66,18 +56,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor theme="9" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor theme="9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -87,67 +71,40 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
+        <color theme="9"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
+        <color theme="9"/>
       </right>
       <top style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
+        <color theme="9"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color theme="9"/>
+      </left>
       <right style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
+        <color theme="9"/>
       </right>
       <top style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
+        <color theme="9"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -489,22 +446,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="12.59765625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>830</v>
-      </c>
-      <c r="B2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1">
         <v>830</v>
       </c>
     </row>
@@ -521,44 +475,14 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1361F2B8-DF1B-4C07-9033-C170FADAC058}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="15.796875" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" s="2">
-        <v>830</v>
-      </c>
-      <c r="B2" s="3">
-        <v>830</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>